--- a/Client/Configs/GameConfig/Datas/wave.xlsx
+++ b/Client/Configs/GameConfig/Datas/wave.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,37 +454,72 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>levelMode</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fixedEnemyLevel</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>levelOffset</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>minEnemyLevel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>maxEnemyLevel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>count</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>spawnDistanceAhead</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>spawnRadius</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>spawnAnchorId</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>isBoss</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>nextWaveDelay</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>spawnEngageMode</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>hpMultiplier</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>attackMultiplier</t>
         </is>
       </c>
     </row>
@@ -526,181 +561,286 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>float</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wave id.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Stage id.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wave index.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spawn mode.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Enemy id.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Enemy level.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Enemy count.</t>
+          <t>c,s</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Distance ahead.</t>
+          <t>c,s</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Spawn radius.</t>
+          <t>c,s</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Fixed anchor id.</t>
+          <t>c,s</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Is boss 1 or 0.</t>
+          <t>c,s</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Next wave delay.</t>
+          <t>c</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Spawn engage mode: RushTeam or HoldPosition.</t>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>c,s</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Wave id.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Stage id.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Wave index.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Spawn mode.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Enemy id.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Legacy/fallback enemy level.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Level mode: Inherit/Fixed/Dynamic.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Fixed enemy level.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Dynamic level offset.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Wave min level override, 0 means stage.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Wave max level override, 0 means stage.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Enemy count.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Distance ahead.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Spawn radius.</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fixed anchor id.</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Is boss 1 or 0.</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Next wave delay.</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Spawn engage mode.</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Wave hp multiplier.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Wave attack multiplier.</t>
         </is>
       </c>
     </row>
@@ -725,25 +865,48 @@
       <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Inherit</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="N5" t="n">
         <v>16</v>
       </c>
-      <c r="J5" t="n">
+      <c r="O5" t="n">
         <v>2.4</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>2</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>RushTeam</t>
         </is>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -767,25 +930,48 @@
       <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Inherit</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="N6" t="n">
         <v>20</v>
       </c>
-      <c r="J6" t="n">
+      <c r="O6" t="n">
         <v>2.8</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>2</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>RushTeam</t>
         </is>
+      </c>
+      <c r="T6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -809,25 +995,48 @@
       <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Inherit</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="N7" t="n">
         <v>24</v>
       </c>
-      <c r="J7" t="n">
+      <c r="O7" t="n">
         <v>3.2</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.5</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>RushTeam</t>
         </is>
+      </c>
+      <c r="T7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="8">
@@ -851,25 +1060,48 @@
       <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Inherit</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="N8" t="n">
         <v>28</v>
       </c>
-      <c r="J8" t="n">
+      <c r="O8" t="n">
         <v>3.4</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>3</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>RushTeam</t>
         </is>
+      </c>
+      <c r="T8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
@@ -893,30 +1125,53 @@
       <c r="G9" t="n">
         <v>3</v>
       </c>
-      <c r="H9" t="n">
-        <v>1</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Inherit</t>
+        </is>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>stage_01_boss_01</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>HoldPosition</t>
         </is>
+      </c>
+      <c r="T9" t="n">
+        <v>10</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>
